--- a/src/models/ML_model_select.xlsx
+++ b/src/models/ML_model_select.xlsx
@@ -485,28 +485,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.919047619047619</v>
+        <v>0.9165784832451499</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8970588235294118</v>
+        <v>0.9088235294117647</v>
       </c>
       <c r="E2" t="n">
-        <v>0.919047619047619</v>
+        <v>0.9165784832451499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8970588235294118</v>
+        <v>0.9088235294117647</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9191189427312775</v>
+        <v>0.9170611958618271</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6702127659574468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9710378893212519</v>
+        <v>0.9684269135180363</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9556149488304093</v>
+        <v>0.9586759868421054</v>
       </c>
     </row>
     <row r="3">
@@ -519,28 +519,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9776014109347443</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9705882352941176</v>
+        <v>0.9654411764705882</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9776014109347443</v>
+        <v>0.9753086419753086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9705882352941176</v>
+        <v>0.9654411764705882</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9777075653852906</v>
+        <v>0.9753607884547694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.8526645768025078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9970949550373418</v>
+        <v>0.9969075147205659</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9901544225146199</v>
+        <v>0.9899830957602339</v>
       </c>
     </row>
     <row r="4">
@@ -556,25 +556,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.986764705882353</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.986764705882353</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9375</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9971959521198831</v>
+        <v>0.9980068987573099</v>
       </c>
     </row>
     <row r="5">
@@ -587,28 +587,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9902998236331569</v>
+        <v>0.989241622574956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9683823529411765</v>
+        <v>0.9669117647058824</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9902998236331569</v>
+        <v>0.989241622574956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9683823529411765</v>
+        <v>0.9669117647058824</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9903627124583845</v>
+        <v>0.9893188583435475</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8599348534201954</v>
+        <v>0.858044164037855</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9997915947357452</v>
+        <v>0.9997284510512023</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9702262655336258</v>
+        <v>0.9796292489035088</v>
       </c>
     </row>
     <row r="6">
@@ -621,28 +621,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9239858906525573</v>
+        <v>0.9209876543209876</v>
       </c>
       <c r="D6" t="n">
-        <v>0.913235294117647</v>
+        <v>0.8875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9239858906525573</v>
+        <v>0.9209876543209876</v>
       </c>
       <c r="F6" t="n">
-        <v>0.913235294117647</v>
+        <v>0.8875</v>
       </c>
       <c r="G6" t="n">
-        <v>0.925030440076535</v>
+        <v>0.9232876712328766</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6827956989247311</v>
+        <v>0.6295399515738499</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9818315401149028</v>
+        <v>0.9820589195897839</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9740097313596491</v>
+        <v>0.9703947368421052</v>
       </c>
     </row>
     <row r="7">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9543209876543209</v>
+        <v>0.9513227513227513</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9404411764705882</v>
+        <v>0.9272058823529412</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9543209876543209</v>
+        <v>0.9513227513227513</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9404411764705882</v>
+        <v>0.9272058823529412</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9549330085261876</v>
+        <v>0.9520999652898299</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7665706051873198</v>
+        <v>0.7195467422096317</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9929514229102707</v>
+        <v>0.9926391882770484</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9820763660453217</v>
+        <v>0.9783500091374269</v>
       </c>
     </row>
     <row r="8">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9987654320987654</v>
+        <v>0.9989417989417989</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9875</v>
+        <v>0.9845588235294118</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9987654320987654</v>
+        <v>0.9989417989417989</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9875</v>
+        <v>0.9845588235294118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9987639060568604</v>
+        <v>0.99894142554693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9415807560137457</v>
+        <v>0.9278350515463918</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9999946498947088</v>
+        <v>0.9999947743157619</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9918648346125731</v>
+        <v>0.9877101608187133</v>
       </c>
     </row>
     <row r="9">
@@ -723,28 +723,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9918871252204585</v>
+        <v>0.9931216931216931</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9852941176470589</v>
+        <v>0.9823529411764705</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9918871252204585</v>
+        <v>0.9931216931216931</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9852941176470589</v>
+        <v>0.9823529411764705</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9919014084507042</v>
+        <v>0.9931325937665082</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9319727891156462</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9996417295770618</v>
+        <v>0.9997002074721063</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9978641264619883</v>
+        <v>0.9971502649853801</v>
       </c>
     </row>
     <row r="10">
@@ -760,25 +760,25 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9904411764705883</v>
+        <v>0.9889705882352942</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9904411764705883</v>
+        <v>0.9889705882352942</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9547038327526133</v>
+        <v>0.9488054607508531</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.998852110745614</v>
+        <v>0.9985551443713451</v>
       </c>
     </row>
     <row r="11">
@@ -794,25 +794,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9897058823529412</v>
+        <v>0.9875</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9897058823529412</v>
+        <v>0.9875</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9513888888888888</v>
+        <v>0.9407665505226481</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9984180829678363</v>
+        <v>0.9949230171783626</v>
       </c>
     </row>
     <row r="12">
@@ -825,28 +825,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0.9998236331569665</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.9875</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.9998236331569665</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.9875</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.9998236020462162</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9452054794520548</v>
+        <v>0.9419795221843005</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.9999999377894734</v>
       </c>
       <c r="J12" t="n">
-        <v>0.998429504751462</v>
+        <v>0.9979212353801169</v>
       </c>
     </row>
     <row r="13">
@@ -859,28 +859,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.991358024691358</v>
+        <v>0.9904761904761905</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9772058823529411</v>
+        <v>0.975</v>
       </c>
       <c r="E13" t="n">
-        <v>0.991358024691358</v>
+        <v>0.9904761904761905</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9772058823529411</v>
+        <v>0.975</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9913899138991389</v>
+        <v>0.9905263157894736</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8976897689768977</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9995760352609265</v>
+        <v>0.9995853668399232</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9964192708333333</v>
+        <v>0.9973787006578947</v>
       </c>
     </row>
   </sheetData>

--- a/src/models/ML_model_select.xlsx
+++ b/src/models/ML_model_select.xlsx
@@ -485,28 +485,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9165784832451499</v>
+        <v>0.9153439153439153</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9088235294117647</v>
+        <v>0.9080882352941176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9165784832451499</v>
+        <v>0.9153439153439153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9088235294117647</v>
+        <v>0.9080882352941176</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9170611958618271</v>
+        <v>0.9156118143459915</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6702127659574468</v>
+        <v>0.6719160104986875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9684269135180363</v>
+        <v>0.9690420512054844</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9586759868421054</v>
+        <v>0.9606747989766082</v>
       </c>
     </row>
     <row r="3">
@@ -519,28 +519,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9753086419753086</v>
+        <v>0.7832451499118166</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9654411764705882</v>
+        <v>0.7522058823529412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9753086419753086</v>
+        <v>0.7832451499118166</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9654411764705882</v>
+        <v>0.7522058823529412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9753607884547694</v>
+        <v>0.7837409818757699</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8526645768025078</v>
+        <v>0.3861566484517304</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9969075147205659</v>
+        <v>0.8698068674200361</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9899830957602339</v>
+        <v>0.8615537052266082</v>
       </c>
     </row>
     <row r="4">
@@ -556,25 +556,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.9845588235294118</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9882352941176471</v>
+        <v>0.9845588235294118</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9452054794520548</v>
+        <v>0.9283276450511946</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9980068987573099</v>
+        <v>0.99808685124269</v>
       </c>
     </row>
     <row r="5">
@@ -587,28 +587,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.989241622574956</v>
+        <v>0.9904761904761905</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9669117647058824</v>
+        <v>0.9727941176470588</v>
       </c>
       <c r="E5" t="n">
-        <v>0.989241622574956</v>
+        <v>0.9904761904761905</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9669117647058824</v>
+        <v>0.9727941176470588</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9893188583435475</v>
+        <v>0.9905329593267883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.858044164037855</v>
+        <v>0.878688524590164</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9997284510512023</v>
+        <v>0.9997741135777585</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9796292489035088</v>
+        <v>0.9780644645467835</v>
       </c>
     </row>
     <row r="6">
@@ -621,28 +621,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9209876543209876</v>
+        <v>0.8865961199294533</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8875</v>
+        <v>0.8522058823529411</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9209876543209876</v>
+        <v>0.8865961199294533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8875</v>
+        <v>0.8522058823529411</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9232876712328766</v>
+        <v>0.8885808352105354</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6295399515738499</v>
+        <v>0.54627539503386</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9820589195897839</v>
+        <v>0.9530849267004471</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9703947368421052</v>
+        <v>0.9396387289839182</v>
       </c>
     </row>
     <row r="7">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9513227513227513</v>
+        <v>0.9585537918871252</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9272058823529412</v>
+        <v>0.9448529411764706</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9513227513227513</v>
+        <v>0.9585537918871252</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9272058823529412</v>
+        <v>0.9448529411764706</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9520999652898299</v>
+        <v>0.959066364744818</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7195467422096317</v>
+        <v>0.7774480712166173</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9926391882770484</v>
+        <v>0.9940883202846753</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9783500091374269</v>
+        <v>0.9806600648757311</v>
       </c>
     </row>
     <row r="8">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9989417989417989</v>
+        <v>0.9102292768959436</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9845588235294118</v>
+        <v>0.8698529411764706</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9989417989417989</v>
+        <v>0.9102292768959436</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9845588235294118</v>
+        <v>0.8698529411764706</v>
       </c>
       <c r="G8" t="n">
-        <v>0.99894142554693</v>
+        <v>0.9119529493167272</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9278350515463918</v>
+        <v>0.5795724465558194</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9999947743157619</v>
+        <v>0.9572260948275058</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9877101608187133</v>
+        <v>0.939347473501462</v>
       </c>
     </row>
     <row r="9">
@@ -723,28 +723,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9931216931216931</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9823529411764705</v>
+        <v>0.9830882352941176</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9931216931216931</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9823529411764705</v>
+        <v>0.9830882352941176</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9931325937665082</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9192982456140351</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9997002074721063</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9971502649853801</v>
+        <v>0.9981154057017544</v>
       </c>
     </row>
     <row r="10">
@@ -760,25 +760,25 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9889705882352942</v>
+        <v>0.9860294117647059</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9889705882352942</v>
+        <v>0.9860294117647059</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9488054607508531</v>
+        <v>0.9342560553633218</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9985551443713451</v>
+        <v>0.9979497898391813</v>
       </c>
     </row>
     <row r="11">
@@ -794,25 +794,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9875</v>
+        <v>0.9830882352941176</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9875</v>
+        <v>0.9830882352941176</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9407665505226481</v>
+        <v>0.9181494661921709</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9949230171783626</v>
+        <v>0.9971445540935673</v>
       </c>
     </row>
     <row r="12">
@@ -825,28 +825,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9998236331569665</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9875</v>
+        <v>0.9838235294117647</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9998236331569665</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9875</v>
+        <v>0.9838235294117647</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9998236020462162</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9419795221843005</v>
+        <v>0.9251700680272109</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9999999377894734</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9979212353801169</v>
+        <v>0.9982410453216375</v>
       </c>
     </row>
     <row r="13">
@@ -859,28 +859,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.9945326278659612</v>
       </c>
       <c r="D13" t="n">
-        <v>0.975</v>
+        <v>0.9772058823529411</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.9945326278659612</v>
       </c>
       <c r="F13" t="n">
-        <v>0.975</v>
+        <v>0.9772058823529411</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9905263157894736</v>
+        <v>0.9945451346120007</v>
       </c>
       <c r="H13" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8983606557377048</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9995853668399232</v>
+        <v>0.99988491052571</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9973787006578947</v>
+        <v>0.9974415204678362</v>
       </c>
     </row>
   </sheetData>

--- a/src/models/ML_model_select.xlsx
+++ b/src/models/ML_model_select.xlsx
@@ -485,28 +485,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9153439153439153</v>
+        <v>0.908994708994709</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9080882352941176</v>
+        <v>0.9058823529411765</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9153439153439153</v>
+        <v>0.908994708994709</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9080882352941176</v>
+        <v>0.9058823529411765</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9156118143459915</v>
+        <v>0.9092827004219409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6719160104986875</v>
+        <v>0.6649214659685864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9690420512054844</v>
+        <v>0.966446005928663</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9606747989766082</v>
+        <v>0.9573167945906432</v>
       </c>
     </row>
     <row r="3">
@@ -519,28 +519,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7832451499118166</v>
+        <v>0.781305114638448</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7522058823529412</v>
+        <v>0.7536764705882353</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7832451499118166</v>
+        <v>0.781305114638448</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7522058823529412</v>
+        <v>0.7536764705882353</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7837409818757699</v>
+        <v>0.7813822284908322</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3861566484517304</v>
+        <v>0.3784786641929499</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8698068674200361</v>
+        <v>0.8716385319559923</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8615537052266082</v>
+        <v>0.8400436312134502</v>
       </c>
     </row>
     <row r="4">
@@ -556,25 +556,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9845588235294118</v>
+        <v>0.986764705882353</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9845588235294118</v>
+        <v>0.986764705882353</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9283276450511946</v>
+        <v>0.9375</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99808685124269</v>
+        <v>0.9977641858552632</v>
       </c>
     </row>
     <row r="5">
@@ -587,28 +587,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.9924162257495591</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9727941176470588</v>
+        <v>0.9661764705882353</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.9924162257495591</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9727941176470588</v>
+        <v>0.9661764705882353</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9905329593267883</v>
+        <v>0.9924601087147116</v>
       </c>
       <c r="H5" t="n">
-        <v>0.878688524590164</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9997741135777585</v>
+        <v>0.9997876132620401</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9780644645467835</v>
+        <v>0.9589986522295322</v>
       </c>
     </row>
     <row r="6">
@@ -621,28 +621,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8865961199294533</v>
+        <v>0.8851851851851852</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8522058823529411</v>
+        <v>0.8661764705882353</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8865961199294533</v>
+        <v>0.8851851851851852</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8522058823529411</v>
+        <v>0.8661764705882353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8885808352105354</v>
+        <v>0.8874675885911841</v>
       </c>
       <c r="H6" t="n">
-        <v>0.54627539503386</v>
+        <v>0.5767441860465116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9530849267004471</v>
+        <v>0.9515872082715117</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9396387289839182</v>
+        <v>0.949812682748538</v>
       </c>
     </row>
     <row r="7">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9585537918871252</v>
+        <v>0.9520282186948854</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9448529411764706</v>
+        <v>0.9360294117647059</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9585537918871252</v>
+        <v>0.9520282186948854</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9448529411764706</v>
+        <v>0.9360294117647059</v>
       </c>
       <c r="G7" t="n">
-        <v>0.959066364744818</v>
+        <v>0.9529411764705882</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7774480712166173</v>
+        <v>0.752136752136752</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9940883202846753</v>
+        <v>0.9925530889081742</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9806600648757311</v>
+        <v>0.978601288377193</v>
       </c>
     </row>
     <row r="8">
@@ -689,28 +689,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9102292768959436</v>
+        <v>0.9088183421516755</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8698529411764706</v>
+        <v>0.8845588235294117</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9102292768959436</v>
+        <v>0.9088183421516755</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8698529411764706</v>
+        <v>0.8845588235294117</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9119529493167272</v>
+        <v>0.9110001721466688</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5795724465558194</v>
+        <v>0.6270783847980997</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9572260948275058</v>
+        <v>0.9571808055641096</v>
       </c>
       <c r="J8" t="n">
-        <v>0.939347473501462</v>
+        <v>0.9487247578581871</v>
       </c>
     </row>
     <row r="9">
@@ -726,25 +726,25 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9830882352941176</v>
+        <v>0.9933823529411765</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9830882352941176</v>
+        <v>0.9933823529411765</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9192982456140351</v>
+        <v>0.9681978798586571</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9981154057017544</v>
+        <v>0.999280427631579</v>
       </c>
     </row>
     <row r="10">
@@ -760,25 +760,25 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9860294117647059</v>
+        <v>0.9875</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9860294117647059</v>
+        <v>0.9875</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9342560553633218</v>
+        <v>0.9399293286219081</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9979497898391813</v>
+        <v>0.9982296235380117</v>
       </c>
     </row>
     <row r="11">
@@ -794,25 +794,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9830882352941176</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9830882352941176</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9181494661921709</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9971445540935673</v>
+        <v>0.9984751918859649</v>
       </c>
     </row>
     <row r="12">
@@ -828,25 +828,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9838235294117647</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9838235294117647</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9251700680272109</v>
+        <v>0.9432624113475179</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9982410453216375</v>
+        <v>0.998977750365497</v>
       </c>
     </row>
     <row r="13">
@@ -859,28 +859,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9945326278659612</v>
+        <v>0.9934744268077601</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9772058823529411</v>
+        <v>0.9786764705882353</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9945326278659612</v>
+        <v>0.9934744268077601</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9772058823529411</v>
+        <v>0.9786764705882353</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9945451346120007</v>
+        <v>0.9934893542143235</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8983606557377048</v>
+        <v>0.9036544850498339</v>
       </c>
       <c r="I13" t="n">
-        <v>0.99988491052571</v>
+        <v>0.9998862169467695</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9974415204678362</v>
+        <v>0.9967505025584795</v>
       </c>
     </row>
   </sheetData>
